--- a/data/trans_orig/IP1003-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1003-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +783,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>5431</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>9850</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>5431</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>2689</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>10651</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101133</t>
+          <t>101090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113301</t>
+          <t>112946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120072</t>
+          <t>119964</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +896,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>222120</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>217701</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>225096</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>95,67%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>98,92%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>222120</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>216900</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>224862</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23526</t>
+          <t>23504</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21959</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23035</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40475</t>
+          <t>41221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229679</t>
+          <t>229701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242408</t>
+          <t>242383</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231797</t>
+          <t>231322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>244062</t>
+          <t>243807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>466486</t>
+          <t>465740</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>483926</t>
+          <t>484085</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>17352</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31793</t>
+          <t>31927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110735</t>
+          <t>110521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121005</t>
+          <t>120875</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122781</t>
+          <t>122959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133593</t>
+          <t>133915</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>237270</t>
+          <t>237136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>252102</t>
+          <t>251711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17002</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25850</t>
+          <t>27595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39179</t>
+          <t>39192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177095</t>
+          <t>176318</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>187187</t>
+          <t>187205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180199</t>
+          <t>178454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193237</t>
+          <t>192428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360967</t>
+          <t>360954</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>377517</t>
+          <t>377817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>30846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51320</t>
+          <t>51436</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40194</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61202</t>
+          <t>60760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76829</t>
+          <t>77445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107294</t>
+          <t>107716</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>629701</t>
+          <t>629585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>648912</t>
+          <t>650175</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>661498</t>
+          <t>661940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>682506</t>
+          <t>683542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1296427</t>
+          <t>1296005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1326892</t>
+          <t>1326276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141491</t>
+          <t>142590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138723</t>
+          <t>139119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143866</t>
+          <t>143864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>283877</t>
+          <t>284187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290129</t>
+          <t>290060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34303</t>
+          <t>35062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217135</t>
+          <t>217836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>228304</t>
+          <t>228789</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>243732</t>
+          <t>243492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256799</t>
+          <t>256716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>466646</t>
+          <t>465887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>482918</t>
+          <t>482301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15933</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>21969</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17545</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34193</t>
+          <t>33700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138901</t>
+          <t>138956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149145</t>
+          <t>149112</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136914</t>
+          <t>136602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149098</t>
+          <t>149553</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>279212</t>
+          <t>279705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295860</t>
+          <t>295777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19462</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>18070</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35241</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151875</t>
+          <t>151694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163462</t>
+          <t>163392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158002</t>
+          <t>158190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169882</t>
+          <t>169828</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314053</t>
+          <t>314124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330926</t>
+          <t>331224</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43089</t>
+          <t>44335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,47 +4067,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35045</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>56959</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>6,1%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>45668</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>34688</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>57298</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65827</t>
+          <t>65552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94505</t>
+          <t>95580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>663212</t>
+          <t>661966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>682046</t>
+          <t>681400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,47 +4180,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>702474</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>691183</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>713097</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>93,9%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>702474</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>690844</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>713454</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1359938</t>
+          <t>1358863</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1388616</t>
+          <t>1388891</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126345</t>
+          <t>126804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131097</t>
+          <t>131089</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119596</t>
+          <t>119042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248986</t>
+          <t>248663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>254607</t>
+          <t>254609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28189</t>
+          <t>27924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197642</t>
+          <t>198054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207067</t>
+          <t>206690</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>238798</t>
+          <t>239132</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>250459</t>
+          <t>250508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>440389</t>
+          <t>440654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>455534</t>
+          <t>455802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20118</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20012</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36363</t>
+          <t>36436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168781</t>
+          <t>168318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180819</t>
+          <t>180160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>168560</t>
+          <t>169676</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180533</t>
+          <t>181260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341108</t>
+          <t>341035</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>358645</t>
+          <t>358573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19531</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31326</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157943</t>
+          <t>157903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168058</t>
+          <t>167501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154392</t>
+          <t>154517</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>166430</t>
+          <t>166260</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>316022</t>
+          <t>316810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332062</t>
+          <t>332347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>23611</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>41695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50166</t>
+          <t>50237</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58482</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86083</t>
+          <t>85532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>660831</t>
+          <t>662676</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>680525</t>
+          <t>680760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694678</t>
+          <t>694607</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>715621</t>
+          <t>715192</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1363132</t>
+          <t>1363683</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1390733</t>
+          <t>1391669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55167</t>
+          <t>55094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58355</t>
+          <t>57619</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114863</t>
+          <t>115216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10890</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>16389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23899</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147578</t>
+          <t>148049</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155951</t>
+          <t>155788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164942</t>
+          <t>165374</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176634</t>
+          <t>176827</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316332</t>
+          <t>316074</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330770</t>
+          <t>330589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28325</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40837</t>
+          <t>40133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156251</t>
+          <t>156490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166935</t>
+          <t>167342</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>183162</t>
+          <t>182845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200563</t>
+          <t>200851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>343723</t>
+          <t>344427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>365351</t>
+          <t>364568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>29756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24706</t>
+          <t>25193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47123</t>
+          <t>47843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42364</t>
+          <t>41892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70447</t>
+          <t>69528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>245954</t>
+          <t>245702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262364</t>
+          <t>262063</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258360</t>
+          <t>257640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>280777</t>
+          <t>280290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>510493</t>
+          <t>511412</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>538576</t>
+          <t>539048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t>27416</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47281</t>
+          <t>50068</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>49293</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80052</t>
+          <t>79927</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82784</t>
+          <t>79215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119073</t>
+          <t>118587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>616603</t>
+          <t>613816</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>637322</t>
+          <t>636468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>680125</t>
+          <t>680250</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710985</t>
+          <t>710884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1304989</t>
+          <t>1305475</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341278</t>
+          <t>1344847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1003-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1003-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7999</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1844</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>519</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5081</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5127</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,74%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3587</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8434</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>117793</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>113381</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120040</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104327</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>101090</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>101044</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>105652</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>117793</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>112946</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>119964</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,05%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>336</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>217701</t>
+          <t>217266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225096</t>
+          <t>224967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14949</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9758</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21232</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16431</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10822</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23504</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10767</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23607</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14949</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9949</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22434</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>22540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41221</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>238807</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>232524</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>243998</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>355</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>236774</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>229701</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>242383</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>229598</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>242438</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,51%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>238807</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>231322</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>243807</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>465740</t>
+          <t>466260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>484085</t>
+          <t>484421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12476</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19134</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10982</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6673</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17027</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7020</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17338</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>8,61%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12476</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7600</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18556</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17352</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31927</t>
+          <t>32192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>129039</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>122381</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>133499</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>116566</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>110521</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>120875</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>110210</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>120528</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>91,39%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>129039</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>122959</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>133915</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>237136</t>
+          <t>236871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251711</t>
+          <t>252122</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18954</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12532</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25958</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11382</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6892</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17779</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17873</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18954</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>13621</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>27595</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39192</t>
+          <t>39359</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>187095</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>180091</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>193517</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>182715</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>176318</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>187205</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>176224</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>187097</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,14%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>187095</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>178454</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>192428</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,8%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360954</t>
+          <t>360787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>377817</t>
+          <t>378095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>39235</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>60973</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>40639</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30846</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>51436</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31291</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>50830</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,97%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>49967</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>39158</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>60760</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77445</t>
+          <t>76611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107716</t>
+          <t>106770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>672733</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>661727</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>683465</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>957</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>640382</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>629585</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>650175</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>630191</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>649730</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>672733</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>661940</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>683542</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1296005</t>
+          <t>1296951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1326276</t>
+          <t>1327110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5493</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>734</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3691</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4059</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>142454</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>139020</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>143866</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>145547</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>142590</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>142222</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>142454</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>139119</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>143864</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>419</t>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284187</t>
+          <t>284309</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290060</t>
+          <t>290058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15907</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10467</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23235</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>9644</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5060</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16013</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5387</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>15641</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,12%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>15907</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10385</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23609</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35062</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>251194</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>243866</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>256634</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,3%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>323</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>224205</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>217836</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>228789</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>218208</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>228462</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,88%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>251194</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>243492</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>256716</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>465887</t>
+          <t>465399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>482301</t>
+          <t>482344</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>233849</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>233849</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>233849</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14740</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9635</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22105</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9869</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5722</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15878</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5785</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16460</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,37%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14740</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9018</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>21969</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17628</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33700</t>
+          <t>34035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>143831</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>136466</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148936</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>144965</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>138956</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>149112</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>138374</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>149049</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,75%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>143831</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>136602</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149553</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>279705</t>
+          <t>279370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295777</t>
+          <t>296040</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12962</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19694</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>12942</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7945</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19643</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7817</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19483</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12962</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8129</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19767</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35170</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>164995</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>158263</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>169957</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>158395</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>151694</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>163392</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>151854</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>163520</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>164995</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>158190</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>169828</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314124</t>
+          <t>314823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331224</t>
+          <t>331176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35965</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>57637</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>33189</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>24901</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44335</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24394</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43668</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,7%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>45668</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>35045</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>56959</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65552</t>
+          <t>65194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95580</t>
+          <t>94771</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>702474</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>690505</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>712177</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>673112</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>661966</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>681400</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>662633</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>681907</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,3%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>702474</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>691183</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>713097</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1358863</t>
+          <t>1359672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1388891</t>
+          <t>1389249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706301</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706301</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706301</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3948</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1789</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4850</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4870</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5122</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>122862</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>120216</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>129865</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>126804</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>131089</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>126784</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>131088</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,3%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>122862</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>119042</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,87%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>393</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248663</t>
+          <t>249145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>254609</t>
+          <t>254680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12185</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7640</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19231</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7010</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3827</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12463</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3774</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12655</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12185</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7553</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18929</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12776</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>245876</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>238830</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>250421</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>322</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>203507</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>198054</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>206690</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>197862</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>206743</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>245876</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>239132</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>250508</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>440654</t>
+          <t>441394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>455802</t>
+          <t>455564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12521</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7129</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19467</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13718</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8739</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20581</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8722</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21608</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,26%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7312</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18896</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36436</t>
+          <t>35932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>176051</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>169105</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>181443</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>175181</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>168318</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>180160</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>167291</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>180177</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,37%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>176051</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>169676</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>181260</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341035</t>
+          <t>341539</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>358573</t>
+          <t>358369</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12592</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7639</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19542</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9616</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5800</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15398</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15690</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12592</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7788</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19531</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30538</t>
+          <t>30368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161456</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>154506</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>166409</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>163685</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>157903</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167501</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>157611</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>167481</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>161456</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>154517</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>166260</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>316810</t>
+          <t>316980</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332347</t>
+          <t>331995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,107 +5989,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>29165</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>49869</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>32132</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23611</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>41695</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>23158</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42850</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,56%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>58078</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>85840</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>38600</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>29652</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>50237</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>70732</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>57546</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>85532</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -6102,107 +6102,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>706244</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>694975</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>715679</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,3%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>672239</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>662676</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>680760</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>661521</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>681213</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,44%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1378483</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1363375</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1391137</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>94,08%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>706244</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>694607</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>715192</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1378483</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1363683</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1391669</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>94,1%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>495</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>252</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>746</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50042</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48137</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>56572</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55094</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56886</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>51234</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50073</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>51486</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60848</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>57619</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61444</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,77%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>222</t>
@@ -6752,22 +6752,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>117420</t>
+          <t>101277</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115216</t>
+          <t>99344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118330</t>
+          <t>102023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>56886</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56886</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>56886</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51486</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51486</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51486</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118330</t>
+          <t>102023</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118330</t>
+          <t>102023</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118330</t>
+          <t>102023</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3755</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11480</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5466</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2680</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10419</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16389</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>150259</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>145445</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>153170</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>153002</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>148049</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>155788</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>172453</t>
+          <t>139066</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165374</t>
+          <t>133969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176827</t>
+          <t>142173</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>325455</t>
+          <t>289324</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316074</t>
+          <t>283768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330589</t>
+          <t>294297</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156925</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156925</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156925</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>158468</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>158468</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>158468</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181763</t>
+          <t>144648</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181763</t>
+          <t>144648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181763</t>
+          <t>144648</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>340231</t>
+          <t>301572</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>340231</t>
+          <t>301572</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>340231</t>
+          <t>301572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16469</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26291</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10451</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5730</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16582</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28642</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28608</t>
+          <t>27577</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19992</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40133</t>
+          <t>37768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>182704</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>172882</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>189269</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>162621</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>156490</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>167342</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>93,96%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>193330</t>
+          <t>163564</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>182845</t>
+          <t>157123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200851</t>
+          <t>167935</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>355952</t>
+          <t>346268</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>344427</t>
+          <t>336077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>364568</t>
+          <t>355117</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199173</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199173</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199173</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211487</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211487</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211487</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384560</t>
+          <t>373845</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384560</t>
+          <t>373845</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384560</t>
+          <t>373845</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34849</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25343</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46925</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20372</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13395</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29756</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34572</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47843</t>
+          <t>29842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54944</t>
+          <t>56027</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41892</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69528</t>
+          <t>70340</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>257796</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>245720</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>267302</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>313</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>255086</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>245702</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>262063</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,6%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>270911</t>
+          <t>235374</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257640</t>
+          <t>226711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>280290</t>
+          <t>242318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>525996</t>
+          <t>493171</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>511412</t>
+          <t>478858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>539048</t>
+          <t>506445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>58479</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45376</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>72397</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>36603</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>27416</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50068</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62635</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49293</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79927</t>
+          <t>50580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>96599</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79215</t>
+          <t>79789</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118587</t>
+          <t>113760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>640801</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>626883</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>653904</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>91,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>887</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>627281</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>613816</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>636468</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,87%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>697542</t>
+          <t>589239</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>680250</t>
+          <t>576779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710884</t>
+          <t>598125</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1324824</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1305475</t>
+          <t>1212879</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1344847</t>
+          <t>1246850</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699280</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699280</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699280</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>663884</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>663884</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>663884</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760177</t>
+          <t>627359</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760177</t>
+          <t>627359</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760177</t>
+          <t>627359</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1424062</t>
+          <t>1326639</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1424062</t>
+          <t>1326639</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1424062</t>
+          <t>1326639</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
